--- a/resultsHPC/Muraro.xlsx
+++ b/resultsHPC/Muraro.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -485,21 +485,21 @@
         <v>64</v>
       </c>
       <c r="B2" t="n">
-        <v>512</v>
+        <v>64</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>&lt;class 'torch_geometric.nn.conv.gcn_conv.GCNConv'&gt;</t>
+          <t>&lt;class 'torch_geometric.nn.conv.sage_conv.SAGEConv'&gt;</t>
         </is>
       </c>
       <c r="D2" t="n">
+        <v>200</v>
+      </c>
+      <c r="E2" t="n">
         <v>500</v>
       </c>
-      <c r="E2" t="n">
-        <v>800</v>
-      </c>
       <c r="F2" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -507,35 +507,35 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>130</v>
+        <v>460</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9240194531613294</v>
+        <v>0.9261422599027844</v>
       </c>
       <c r="J2" t="n">
-        <v>0.893582023499317</v>
+        <v>0.894535536773767</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B3" t="n">
         <v>128</v>
       </c>
-      <c r="B3" t="n">
-        <v>32</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>&lt;class 'torch_geometric.nn.conv.sage_conv.SAGEConv'&gt;</t>
+          <t>&lt;class 'torch_geometric.nn.conv.gcn_conv.GCNConv'&gt;</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>500</v>
+        <v>200</v>
       </c>
       <c r="E3" t="n">
         <v>500</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0001</v>
+        <v>0.001</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -543,18 +543,18 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9305482419418576</v>
+        <v>0.9248508267444971</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8933929739057624</v>
+        <v>0.8933630761774518</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>512</v>
+        <v>128</v>
       </c>
       <c r="B4" t="n">
         <v>128</v>
@@ -565,10 +565,10 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>200</v>
+      </c>
+      <c r="E4" t="n">
         <v>500</v>
-      </c>
-      <c r="E4" t="n">
-        <v>800</v>
       </c>
       <c r="F4" t="n">
         <v>0.0001</v>
@@ -582,10 +582,10 @@
         <v>30</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9239107225240802</v>
+        <v>0.9233331949008207</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8932679947473307</v>
+        <v>0.8930628719489394</v>
       </c>
     </row>
   </sheetData>
